--- a/public/Excel_Core1_Starter.xlsx
+++ b/public/Excel_Core1_Starter.xlsx
@@ -10,7 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExpenseData" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,25 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="007A4100"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -59,22 +46,16 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00888888"/>
-      <sz val="9"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -88,7 +69,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DAEEF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,30 +109,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,365 +518,341 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A3:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>[INSTRUCTION] DASHBOARD — Merge A1:F1 for title. Freeze row 1 and column A. AutoFill months Jan-Dec. Insert 2 rows above for title. Format revenue cells as Currency. Apply conditional formatting (red) to negative profit months. Name range 'MonthlyRevenue'. Apply Office theme. Set print area A1:F13 Landscape.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Desert Bloom Florist — 2026 Financial Dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="1" ht="24" customHeight="1"/>
+    <row r="2" ht="16" customHeight="1"/>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>January</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Monthly Revenue</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="n">
         <v>42000</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>38500</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>44200</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="4" t="n">
         <v>40100</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="4" t="n">
         <v>46800</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="4" t="n">
         <v>51200</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="4" t="n">
         <v>48900</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="4" t="n">
         <v>52100</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="4" t="n">
         <v>49300</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="4" t="n">
         <v>44600</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="L4" s="4" t="n">
         <v>38200</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="M4" s="4" t="n">
         <v>55400</v>
       </c>
+      <c r="N4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Monthly Expenses</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>28000</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>26500</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>30200</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="4" t="n">
         <v>27800</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="4" t="n">
         <v>31500</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="4" t="n">
         <v>34200</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="4" t="n">
         <v>33100</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="4" t="n">
         <v>35800</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="4" t="n">
         <v>32400</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="K5" s="4" t="n">
         <v>29800</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L5" s="4" t="n">
         <v>27200</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="M5" s="4" t="n">
         <v>38100</v>
       </c>
+      <c r="N5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Net Profit</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr"/>
-      <c r="K6" s="6" t="inlineStr"/>
-      <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>SUMMARY FORMULAS</t>
-        </is>
-      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Profit Status</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr"/>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Average Monthly Revenue</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Total Revenue (SUM)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Average Monthly Revenue (AVERAGE)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Best Month (MAX)</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Worst Month (MIN)</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Months Recorded (COUNT)</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Profitable Months (COUNTIF)</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Revenue where Profit &gt; $2000 (SUMIF)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr"/>
+      <c r="B15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Revenue where Profit &gt; $2,000 (SUMIF)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Month+Year Label — January (CONCAT)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Report Date (TODAY)</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Report Year (YEAR)</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Report Month (MONTH)</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>PRODUCT CATEGORY LOOKUP (VLOOKUP + IFERROR)</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>PRODUCT LOOKUP (VLOOKUP + IFERROR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Category (VLOOKUP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Rose Bouquet</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Tropical Arrangement</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="B24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Wedding Package</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Succulent Gift Box</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Corporate Weekly</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>UnknownProduct</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Month+Year Label (CONCAT)</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr"/>
-      <c r="C29" s="6" t="inlineStr"/>
-      <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="6" t="inlineStr"/>
-      <c r="H29" s="6" t="inlineStr"/>
-      <c r="I29" s="6" t="inlineStr"/>
-      <c r="J29" s="6" t="inlineStr"/>
-      <c r="K29" s="6" t="inlineStr"/>
-      <c r="L29" s="6" t="inlineStr"/>
-      <c r="M29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Profit Status (IF)</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr"/>
-      <c r="C30" s="6" t="inlineStr"/>
-      <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr"/>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="6" t="inlineStr"/>
-      <c r="I30" s="6" t="inlineStr"/>
-      <c r="J30" s="6" t="inlineStr"/>
-      <c r="K30" s="6" t="inlineStr"/>
-      <c r="L30" s="6" t="inlineStr"/>
-      <c r="M30" s="6" t="inlineStr"/>
+      <c r="B28" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -876,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -885,237 +872,227 @@
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[INSTRUCTION] PRODUCTS — Convert this range to an Excel Table. Apply blue Medium table style. Add Total Row for units and revenue. Filter for revenue &gt; $5,000. Sort by revenue largest to smallest. Remove duplicates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Units Sold</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Rose Bouquet</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Floral</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C2" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D2" s="13" t="n">
         <v>14200</v>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Tropical Arrangement</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Exotic</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>10680</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Tropical Arrangement</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Exotic</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>89</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>10680</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
           <t>Wedding Package</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C4" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D4" s="13" t="n">
         <v>27200</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Succulent Gift Box</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Gift</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>201</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>8040</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Succulent Gift Box</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
+          <t>Corporate Weekly</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>16380</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Holiday Special</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Orchid Centerpiece</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>8710</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Sympathy Arrangement</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Floral</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>5720</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Baby Welcome Basket</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Gift</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
-        <v>201</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>8040</v>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Corporate Weekly</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Corporate</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>16380</v>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Holiday Special</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Seasonal</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>115</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>9200</v>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Orchid Centerpiece</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="C10" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>7440</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Anniversary Bundle</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>11200</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Rose Bouquet</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Floral</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
-        <v>67</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>8710</v>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Sympathy Arrangement</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Floral</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>44</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>5720</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Baby Welcome Basket</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Gift</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>93</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>7440</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Anniversary Bundle</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Events</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>11200</v>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Rose Bouquet</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Floral</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n">
+      <c r="C12" s="17" t="n">
         <v>142</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D12" s="18" t="n">
         <v>14200</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1126,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1134,148 +1111,141 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>Product Category Reference Table</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Product Category Reference — use for VLOOKUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Rose Bouquet</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Floral</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Tropical Arrangement</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Exotic</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Wedding Package</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Succulent Gift Box</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Gift</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Corporate Weekly</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Corporate</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Holiday Special</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Seasonal</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Orchid Centerpiece</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Floral</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Sympathy Arrangement</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Floral</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Baby Welcome Basket</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Gift</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Anniversary Bundle</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>[Students use VLOOKUP to pull Category from this table into Dashboard sheet]</t>
         </is>
       </c>
     </row>
@@ -1285,287 +1255,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>[INSTRUCTION] IMPORT TASK — In real Excel, import ExpenseData.csv using Data → From Text/CSV. This sheet shows what the imported data looks like.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Supplies</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>8200</v>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Nevada Floral Supply</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>12400</v>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>4800</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Desert Properties LLC</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Supplies</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>7800</v>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Nevada Floral Supply</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>11900</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>4800</v>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Desert Properties LLC</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Supplies</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>9200</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Nevada Floral Supply</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>13600</v>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>4800</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Desert Properties LLC</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>